--- a/scripts/simulations/resultados_simulacion/Grupo3_Mezclas/mse_puntual_mezcla_mw_n250.xlsx
+++ b/scripts/simulations/resultados_simulacion/Grupo3_Mezclas/mse_puntual_mezcla_mw_n250.xlsx
@@ -410,20 +410,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E2">
-        <v>0.00135965018331622</v>
+        <v>0.0002198004370235329</v>
       </c>
       <c r="F2">
-        <v>0.0008237288360130418</v>
+        <v>0.0003142575336742019</v>
       </c>
       <c r="G2">
-        <v>0.0007462006970381917</v>
+        <v>0.000287670281317914</v>
       </c>
       <c r="H2">
-        <v>0.001880652038340435</v>
+        <v>0.0001851928071997454</v>
       </c>
     </row>
     <row r="3">
@@ -440,20 +440,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E3">
-        <v>0.0002198004370235329</v>
+        <v>0.001367342157441164</v>
       </c>
       <c r="F3">
-        <v>0.0003142575336742019</v>
+        <v>0.0008587072801106616</v>
       </c>
       <c r="G3">
-        <v>0.000287670281317914</v>
+        <v>0.0007543270054270918</v>
       </c>
       <c r="H3">
-        <v>0.0001851928071997454</v>
+        <v>0.002024621556827443</v>
       </c>
     </row>
     <row r="4">
@@ -470,20 +470,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E4">
-        <v>0.001367356673779537</v>
+        <v>0.0009398891952965015</v>
       </c>
       <c r="F4">
-        <v>0.0008587118791653845</v>
+        <v>0.0003957564787533137</v>
       </c>
       <c r="G4">
-        <v>0.0007543386458092882</v>
+        <v>0.0003706258313070147</v>
       </c>
       <c r="H4">
-        <v>0.002022485721700143</v>
+        <v>0.001256198803348367</v>
       </c>
     </row>
     <row r="5">
@@ -500,20 +500,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E5">
-        <v>0.0009398891952965003</v>
+        <v>0.00135965018331622</v>
       </c>
       <c r="F5">
-        <v>0.0003957564787533132</v>
+        <v>0.0008237288360130418</v>
       </c>
       <c r="G5">
-        <v>0.0003706258313070144</v>
+        <v>0.0007462006970381917</v>
       </c>
       <c r="H5">
-        <v>0.001256198803348366</v>
+        <v>0.001880652038340435</v>
       </c>
     </row>
     <row r="6">
@@ -590,20 +590,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E8">
-        <v>0.04288886396016049</v>
+        <v>0.05298125093290391</v>
       </c>
       <c r="F8">
-        <v>0.01550631808659477</v>
+        <v>0.01507392431828206</v>
       </c>
       <c r="G8">
-        <v>0.04192442924657661</v>
+        <v>0.049623355027376</v>
       </c>
       <c r="H8">
-        <v>0.03377307769079837</v>
+        <v>0.03860087423641449</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E9">
-        <v>0.007467067601045646</v>
+        <v>0.04215330466584013</v>
       </c>
       <c r="F9">
-        <v>0.002022073170181422</v>
+        <v>0.01425730999652019</v>
       </c>
       <c r="G9">
-        <v>0.006874663122250838</v>
+        <v>0.04131287962529157</v>
       </c>
       <c r="H9">
-        <v>0.008934326014867626</v>
+        <v>0.03422912748079536</v>
       </c>
     </row>
     <row r="10">
@@ -650,20 +650,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E10">
-        <v>0.002152927134705115</v>
+        <v>0.04288886396016049</v>
       </c>
       <c r="F10">
-        <v>0.006344874802756745</v>
+        <v>0.01550631808659466</v>
       </c>
       <c r="G10">
-        <v>0.002366210796790801</v>
+        <v>0.04192442924657654</v>
       </c>
       <c r="H10">
-        <v>0.005916912141264027</v>
+        <v>0.03377307769079842</v>
       </c>
     </row>
     <row r="11">
@@ -680,20 +680,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E11">
-        <v>0.04288886396016049</v>
+        <v>0.04172342713752492</v>
       </c>
       <c r="F11">
-        <v>0.01550631808659466</v>
+        <v>0.01496189595554659</v>
       </c>
       <c r="G11">
-        <v>0.04192442924657654</v>
+        <v>0.04098692575784033</v>
       </c>
       <c r="H11">
-        <v>0.03377307769079842</v>
+        <v>0.03522178823974768</v>
       </c>
     </row>
     <row r="12">
@@ -710,20 +710,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E12">
-        <v>0.001989668510307701</v>
+        <v>0.05231135746016845</v>
       </c>
       <c r="F12">
-        <v>0.006089299509083744</v>
+        <v>0.01442494959631372</v>
       </c>
       <c r="G12">
-        <v>0.002272152062496244</v>
+        <v>0.04901863869868122</v>
       </c>
       <c r="H12">
-        <v>0.005922808632233144</v>
+        <v>0.03794849685431078</v>
       </c>
     </row>
     <row r="13">
@@ -770,20 +770,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E14">
-        <v>0.001453619838359723</v>
+        <v>0.0003158859089957163</v>
       </c>
       <c r="F14">
-        <v>0.0009797131278205915</v>
+        <v>0.0004496928052484816</v>
       </c>
       <c r="G14">
-        <v>0.0008706714167480489</v>
+        <v>0.000410587834663607</v>
       </c>
       <c r="H14">
-        <v>0.00208760991868939</v>
+        <v>0.0003015132242484363</v>
       </c>
     </row>
     <row r="15">
@@ -800,20 +800,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E15">
-        <v>0.0003158859089957163</v>
+        <v>0.001350330385855288</v>
       </c>
       <c r="F15">
-        <v>0.0004496928052484816</v>
+        <v>0.0009198055031648813</v>
       </c>
       <c r="G15">
-        <v>0.000410587834663607</v>
+        <v>0.0007849490674687374</v>
       </c>
       <c r="H15">
-        <v>0.0003015132242484363</v>
+        <v>0.002310675197119241</v>
       </c>
     </row>
     <row r="16">
@@ -830,20 +830,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E16">
-        <v>0.001350344123924515</v>
+        <v>0.0009435167576065399</v>
       </c>
       <c r="F16">
-        <v>0.0009198056152234257</v>
+        <v>0.0003924713296652675</v>
       </c>
       <c r="G16">
-        <v>0.0007849571652562896</v>
+        <v>0.000369582611354722</v>
       </c>
       <c r="H16">
-        <v>0.002310853309514905</v>
+        <v>0.00122617396768186</v>
       </c>
     </row>
     <row r="17">
@@ -860,20 +860,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E17">
-        <v>0.0009435167576065394</v>
+        <v>0.001453619838359723</v>
       </c>
       <c r="F17">
-        <v>0.0003924713296652669</v>
+        <v>0.0009797131278205915</v>
       </c>
       <c r="G17">
-        <v>0.0003695826113547214</v>
+        <v>0.0008706714167480489</v>
       </c>
       <c r="H17">
-        <v>0.001226173967681859</v>
+        <v>0.00208760991868939</v>
       </c>
     </row>
     <row r="18">
@@ -950,20 +950,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E20">
-        <v>0.04279933329107364</v>
+        <v>0.05223340010129595</v>
       </c>
       <c r="F20">
-        <v>0.01466453781387972</v>
+        <v>0.01568309939142348</v>
       </c>
       <c r="G20">
-        <v>0.04160192489360247</v>
+        <v>0.04881947429533982</v>
       </c>
       <c r="H20">
-        <v>0.03304498234961022</v>
+        <v>0.03846248484256212</v>
       </c>
     </row>
     <row r="21">
@@ -980,20 +980,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E21">
-        <v>0.008015896927404375</v>
+        <v>0.04237399293754132</v>
       </c>
       <c r="F21">
-        <v>0.002453028943366245</v>
+        <v>0.01511151219307879</v>
       </c>
       <c r="G21">
-        <v>0.007409895036132764</v>
+        <v>0.04180451699483517</v>
       </c>
       <c r="H21">
-        <v>0.00915770273827818</v>
+        <v>0.0348233422596349</v>
       </c>
     </row>
     <row r="22">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E22">
-        <v>0.002290200232978261</v>
+        <v>0.04279933329107368</v>
       </c>
       <c r="F22">
-        <v>0.006350707101513876</v>
+        <v>0.01466453781387968</v>
       </c>
       <c r="G22">
-        <v>0.002575505093381615</v>
+        <v>0.04160192489360249</v>
       </c>
       <c r="H22">
-        <v>0.006125799823414285</v>
+        <v>0.03304498234961026</v>
       </c>
     </row>
     <row r="23">
@@ -1040,20 +1040,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E23">
-        <v>0.04279933329107368</v>
+        <v>0.04282179447911483</v>
       </c>
       <c r="F23">
-        <v>0.01466453781387968</v>
+        <v>0.0160848713002111</v>
       </c>
       <c r="G23">
-        <v>0.04160192489360249</v>
+        <v>0.04219311403457553</v>
       </c>
       <c r="H23">
-        <v>0.03304498234961026</v>
+        <v>0.03559949724482163</v>
       </c>
     </row>
     <row r="24">
@@ -1070,20 +1070,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E24">
-        <v>0.002438175869130726</v>
+        <v>0.05367718797604936</v>
       </c>
       <c r="F24">
-        <v>0.006474523443200032</v>
+        <v>0.01534138047577853</v>
       </c>
       <c r="G24">
-        <v>0.002712437084869816</v>
+        <v>0.05022651760876299</v>
       </c>
       <c r="H24">
-        <v>0.006357111233915538</v>
+        <v>0.03795464246808466</v>
       </c>
     </row>
     <row r="25">
@@ -1130,20 +1130,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="E26">
-        <v>0.002886190248281412</v>
+        <v>0.001657700694100853</v>
       </c>
       <c r="F26">
-        <v>0.003123066379562029</v>
+        <v>0.002173105224128322</v>
       </c>
       <c r="G26">
-        <v>0.002892325582794553</v>
+        <v>0.002102455663276531</v>
       </c>
       <c r="H26">
-        <v>0.004487760667718288</v>
+        <v>0.001134922127592083</v>
       </c>
     </row>
     <row r="27">
@@ -1160,20 +1160,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Moda_Izq</t>
         </is>
       </c>
       <c r="E27">
-        <v>0.001657700694100853</v>
+        <v>0.002731594412251289</v>
       </c>
       <c r="F27">
-        <v>0.002173105224128322</v>
+        <v>0.002860472943024672</v>
       </c>
       <c r="G27">
-        <v>0.002102455663276531</v>
+        <v>0.002703484086513981</v>
       </c>
       <c r="H27">
-        <v>0.001134922127592083</v>
+        <v>0.004174232828695907</v>
       </c>
     </row>
     <row r="28">
@@ -1190,20 +1190,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Valle_Central</t>
         </is>
       </c>
       <c r="E28">
-        <v>0.002731696065616631</v>
+        <v>0.0009430490122687557</v>
       </c>
       <c r="F28">
-        <v>0.002860587669614662</v>
+        <v>0.0004560931628855044</v>
       </c>
       <c r="G28">
-        <v>0.002703610993530815</v>
+        <v>0.0004412183702531185</v>
       </c>
       <c r="H28">
-        <v>0.004174328155629365</v>
+        <v>0.002781213646956311</v>
       </c>
     </row>
     <row r="29">
@@ -1220,20 +1220,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Moda_Der</t>
         </is>
       </c>
       <c r="E29">
-        <v>0.0009430490122687548</v>
+        <v>0.002886190248281412</v>
       </c>
       <c r="F29">
-        <v>0.0004560931628855039</v>
+        <v>0.003123066379562029</v>
       </c>
       <c r="G29">
-        <v>0.0004412183702531182</v>
+        <v>0.002892325582794553</v>
       </c>
       <c r="H29">
-        <v>0.00278121364695631</v>
+        <v>0.004487760667718288</v>
       </c>
     </row>
     <row r="30">
@@ -1310,20 +1310,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Moda</t>
+          <t>Garra_1</t>
         </is>
       </c>
       <c r="E32">
-        <v>0.04679085548185118</v>
+        <v>0.05806866801686378</v>
       </c>
       <c r="F32">
-        <v>0.02550935961752902</v>
+        <v>0.03579681152208909</v>
       </c>
       <c r="G32">
-        <v>0.04406363331092751</v>
+        <v>0.05369345283089592</v>
       </c>
       <c r="H32">
-        <v>0.07148064735864851</v>
+        <v>0.07068685600094739</v>
       </c>
     </row>
     <row r="33">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>Garra_2</t>
         </is>
       </c>
       <c r="E33">
-        <v>0.0120589478795622</v>
+        <v>0.04602143626915248</v>
       </c>
       <c r="F33">
-        <v>0.005218716111023397</v>
+        <v>0.02473796877658503</v>
       </c>
       <c r="G33">
-        <v>0.01010944723280493</v>
+        <v>0.04352637863775703</v>
       </c>
       <c r="H33">
-        <v>0.01043829404969725</v>
+        <v>0.07056679016251728</v>
       </c>
     </row>
     <row r="34">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Garra_3</t>
         </is>
       </c>
       <c r="E34">
-        <v>0.007840655020998427</v>
+        <v>0.04679085548185115</v>
       </c>
       <c r="F34">
-        <v>0.01390875491349864</v>
+        <v>0.02550935961752933</v>
       </c>
       <c r="G34">
-        <v>0.009151396874727314</v>
+        <v>0.0440636333109276</v>
       </c>
       <c r="H34">
-        <v>0.01316984242787282</v>
+        <v>0.07148064735864849</v>
       </c>
     </row>
     <row r="35">
@@ -1400,20 +1400,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mediana</t>
+          <t>Garra_4</t>
         </is>
       </c>
       <c r="E35">
-        <v>0.04679085548185115</v>
+        <v>0.04685828159024634</v>
       </c>
       <c r="F35">
-        <v>0.02550935961752933</v>
+        <v>0.026578955357753</v>
       </c>
       <c r="G35">
-        <v>0.0440636333109276</v>
+        <v>0.0437899710585086</v>
       </c>
       <c r="H35">
-        <v>0.07148064735864849</v>
+        <v>0.07130752207950369</v>
       </c>
     </row>
     <row r="36">
@@ -1430,20 +1430,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Garra_5</t>
         </is>
       </c>
       <c r="E36">
-        <v>0.00774945204671651</v>
+        <v>0.06099954203018967</v>
       </c>
       <c r="F36">
-        <v>0.01410701312919155</v>
+        <v>0.03799115082895588</v>
       </c>
       <c r="G36">
-        <v>0.008749614382438658</v>
+        <v>0.05616283602363094</v>
       </c>
       <c r="H36">
-        <v>0.01336615128152928</v>
+        <v>0.07379294748022182</v>
       </c>
     </row>
     <row r="37">
